--- a/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-MedicationDispense.xlsx
+++ b/tiflow-xborder/build/0.9.0/StructureDefinition-GEM-ERPEU-PR-MedicationDispense.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2924" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2920" uniqueCount="522">
   <si>
     <t>Property</t>
   </si>
@@ -439,7 +439,7 @@
     <t>MedicationDispense.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -477,7 +477,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -511,7 +511,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -554,7 +554,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -730,10 +730,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
+    <t>External identifier</t>
   </si>
   <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
@@ -751,9 +748,6 @@
 </t>
   </si>
   <si>
-    <t>External identifier</t>
-  </si>
-  <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="https://gematik.de/fhir/erp/NamingSystem/GEM_ERP_NS_PrescriptionId"/&gt;
 &lt;/valueIdentifier&gt;</t>
@@ -762,7 +756,7 @@
     <t>MedicationDispense.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure)
+    <t xml:space="preserve">Reference(Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -800,9 +794,6 @@
     <t>required</t>
   </si>
   <si>
-    <t>A coded concept specifying the state of the dispense event.</t>
-  </si>
-  <si>
     <t>https://gematik.de/fhir/terminology/ValueSet/ti-medication-dispense-status-vs</t>
   </si>
   <si>
@@ -822,7 +813,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.0.1)</t>
   </si>
   <si>
     <t>Why a dispense was not performed</t>
@@ -834,7 +825,7 @@
     <t>A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -971,7 +962,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -982,6 +973,12 @@
   <si>
     <t xml:space="preserve">Identifier {http://fhir.de/StructureDefinition/identifier-kvid-10}
 </t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
   </si>
   <si>
     <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
@@ -1014,7 +1011,7 @@
     <t>MedicationDispense.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1033,7 +1030,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1109,7 +1106,7 @@
     <t>A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1137,7 +1134,7 @@
     <t>MedicationDispense.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1153,7 +1150,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1193,12 +1190,6 @@
     <t>MedicationDispense.authorizingPrescription.identifier</t>
   </si>
   <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
     <t>MedicationDispense.authorizingPrescription.display</t>
   </si>
   <si>
@@ -1226,7 +1217,7 @@
     <t>MedicationDispense.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1464,7 +1455,7 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1)
 </t>
   </si>
   <si>
@@ -1519,123 +1510,6 @@
 The pharmacist reviews the medication order prior to dispense and updates the dosageInstruction based on the actual product being dispensed.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-DosageStructuredOrFreeTextWarning:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (text.exists() and timing.empty() and doseAndRate.empty()) or
-  (text.empty() and (timing.exists() or doseAndRate.exists()))
-)
-}DosageStructuredRequiresBoth:Wenn eine strukturierte Dosierungsangabe erfolgt, müssen sowohl timing als auch doseAndRate angegeben werden. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (timing.exists() implies doseAndRate.exists()) and
-  (doseAndRate.exists() implies timing.exists())
-)
-}DosageDoseUnitSameCode:Die Dosiereinheit muss über alle Dosierungen gleich sein. {(%resource.ofType(MedicationRequest).dosageInstruction | ofType(MedicationDispense).dosageInstruction | ofType(MedicationStatement).dosage).all(
-doseAndRate.exists() implies
-  (
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Quantity).code | 
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).low.code | 
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).high.code
-  ).distinct().count() = 1
-)}DosageWarnungViererschemaInText:Hinweis: In Dosage.text wurde ein Viererschema (z. B. 1-1-1-1) erkannt. Bitte prüfen, ob dies strukturiert abgebildet werden kann. {text.exists() implies text.matches('.*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\d+.*').not()}FreeTextSingleDosageOnlyWarning:Wenn eine Dosierung als reiner Freitext angegeben ist, soll nur genau ein Dosage-Element existieren. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
-)
-implies
-(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).count() = 1
-)}DosageStructuredOrFreeText:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (text.exists() and timing.empty() and doseAndRate.empty()) or
-  (text.empty() and (timing.exists() or doseAndRate.exists()))
-)
-}DosageStructuredRequiresGeneratedText:Liegt eine strukturierte Dosierungsangabe vor (timing und doseAndRate belegt, text leer), muss die Extension GeneratedDosageInstructionsMeta vorhanden sein. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(timing.exists() and doseAndRate.exists() and text.empty())
-)
-implies
-(
-%resource.extension.where(
-  url = 'http://ig.fhir.de/igs/medication/StructureDefinition/GeneratedDosageInstructionsMeta'
-).exists() and
-(
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-  ).exists() or
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-  ).exists() or
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-  ).exists()
-)
-)
-}FreeTextSingleDosageOnly:Wenn eine Dosierung als reiner Freitext angegeben ist, darf nur genau ein Dosage-Element existieren. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
-)
-implies
-(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).count() = 1
-)}FreeTextMatchesRenderedText:Wenn eine Dosierung als reiner Freitext angegeben ist (text vorhanden, timing und doseAndRate leer) UND die Extension renderedDosageInstruction befüllt ist, muss der Wert in dosageInstruction.text mit dem Wert in der Extension übereinstimmen. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).where(text.exists() and timing.empty() and doseAndRate.empty()).exists()
-)
-implies
-(
-  (
-    %resource.ofType(MedicationRequest).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-      ).value = %resource.dosageInstruction.text
-    )
-  ) or
-  (
-    %resource.ofType(MedicationDispense).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-      ).value = %resource.dosageInstruction.text
-    )
-  ) or
-  (
-    %resource.ofType(MedicationStatement).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-      ).value = %resource.dosage.text
-    )
-  )
-)}</t>
-  </si>
-  <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
   </si>
   <si>
@@ -1724,7 +1598,7 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1747,7 +1621,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -1766,7 +1640,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -4143,7 +4017,7 @@
         <v>195</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4170,9 +4044,7 @@
       <c r="M18" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4230,7 +4102,7 @@
         <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>117</v>
@@ -4239,7 +4111,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -4262,7 +4134,7 @@
         <v>200</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4289,9 +4161,7 @@
       <c r="M19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N19" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4381,7 +4251,7 @@
         <v>205</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4408,9 +4278,7 @@
       <c r="M20" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N20" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -4468,7 +4336,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -4759,7 +4627,7 @@
         <v>228</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>218</v>
@@ -4773,7 +4641,7 @@
         <v>78</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>78</v>
@@ -4844,13 +4712,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>78</v>
@@ -4872,10 +4740,10 @@
         <v>78</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>217</v>
@@ -4892,7 +4760,7 @@
         <v>78</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>78</v>
@@ -4963,10 +4831,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4989,16 +4857,16 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5048,7 +4916,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5060,13 +4928,13 @@
         <v>150</v>
       </c>
       <c r="AJ25" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>78</v>
@@ -5080,10 +4948,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5109,13 +4977,13 @@
         <v>167</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5123,7 +4991,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>78</v>
@@ -5141,13 +5009,11 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
@@ -5165,7 +5031,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>88</v>
@@ -5180,16 +5046,16 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>78</v>
@@ -5197,10 +5063,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5223,13 +5089,13 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5259,10 +5125,10 @@
         <v>157</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5280,7 +5146,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5295,10 +5161,10 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5312,10 +5178,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5338,16 +5204,16 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5373,13 +5239,13 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -5397,7 +5263,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5415,7 +5281,7 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
@@ -5424,15 +5290,15 @@
         <v>78</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5455,16 +5321,16 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5514,7 +5380,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>88</v>
@@ -5529,27 +5395,27 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5572,16 +5438,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5631,7 +5497,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5643,30 +5509,30 @@
         <v>150</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5778,10 +5644,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5895,10 +5761,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5924,13 +5790,13 @@
         <v>102</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5980,7 +5846,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5989,7 +5855,7 @@
         <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>100</v>
@@ -6012,10 +5878,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6041,13 +5907,13 @@
         <v>130</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6076,10 +5942,10 @@
         <v>146</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>78</v>
@@ -6097,7 +5963,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6129,10 +5995,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6155,16 +6021,16 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6214,7 +6080,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6232,7 +6098,7 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>78</v>
@@ -6246,10 +6112,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6275,13 +6141,13 @@
         <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6331,7 +6197,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6363,10 +6229,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6389,16 +6255,16 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>319</v>
-      </c>
       <c r="N37" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6448,7 +6314,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6460,13 +6326,13 @@
         <v>150</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>78</v>
@@ -6480,10 +6346,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6506,16 +6372,16 @@
         <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>325</v>
-      </c>
       <c r="N38" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6565,7 +6431,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6577,16 +6443,16 @@
         <v>150</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6597,10 +6463,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6623,13 +6489,13 @@
         <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6680,7 +6546,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6695,10 +6561,10 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>78</v>
@@ -6712,10 +6578,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6827,10 +6693,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6944,14 +6810,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6973,10 +6839,10 @@
         <v>109</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>112</v>
@@ -7031,7 +6897,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7063,10 +6929,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7089,19 +6955,19 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -7129,11 +6995,11 @@
         <v>157</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>347</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
       </c>
@@ -7150,7 +7016,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7168,7 +7034,7 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>78</v>
@@ -7177,15 +7043,15 @@
         <v>78</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7208,16 +7074,16 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>352</v>
-      </c>
       <c r="N44" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7267,7 +7133,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -7279,13 +7145,13 @@
         <v>150</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7299,10 +7165,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7325,16 +7191,16 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="N45" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7384,7 +7250,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7396,13 +7262,13 @@
         <v>150</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7416,10 +7282,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7442,16 +7308,16 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7501,7 +7367,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7513,30 +7379,30 @@
         <v>150</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>368</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7648,10 +7514,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7765,10 +7631,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7794,13 +7660,13 @@
         <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7850,7 +7716,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7859,7 +7725,7 @@
         <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>100</v>
@@ -7882,10 +7748,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7911,13 +7777,13 @@
         <v>130</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7946,10 +7812,10 @@
         <v>146</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -7967,7 +7833,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7999,10 +7865,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8028,13 +7894,13 @@
         <v>215</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>374</v>
+        <v>305</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>375</v>
+        <v>306</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8084,7 +7950,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8102,7 +7968,7 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>78</v>
@@ -8116,10 +7982,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8145,13 +8011,13 @@
         <v>102</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8201,7 +8067,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8233,10 +8099,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8259,16 +8125,16 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8297,10 +8163,10 @@
         <v>157</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8318,7 +8184,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8336,24 +8202,24 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8376,16 +8242,16 @@
         <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8435,7 +8301,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8447,30 +8313,30 @@
         <v>150</v>
       </c>
       <c r="AJ54" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AO54" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>392</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8582,10 +8448,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8699,10 +8565,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8725,19 +8591,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8786,7 +8652,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8804,7 +8670,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8813,15 +8679,15 @@
         <v>78</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8847,65 +8713,65 @@
         <v>167</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q58" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="R58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="P58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q58" t="s" s="2">
+      <c r="AA58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="R58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8923,7 +8789,7 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8932,15 +8798,15 @@
         <v>78</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8966,14 +8832,14 @@
         <v>102</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -9022,7 +8888,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9040,7 +8906,7 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>78</v>
@@ -9049,15 +8915,15 @@
         <v>78</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9083,14 +8949,14 @@
         <v>130</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9139,7 +9005,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9148,7 +9014,7 @@
         <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>100</v>
@@ -9157,7 +9023,7 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9166,15 +9032,15 @@
         <v>78</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9200,16 +9066,16 @@
         <v>167</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9258,7 +9124,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9276,7 +9142,7 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -9285,15 +9151,15 @@
         <v>78</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9316,16 +9182,16 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9375,7 +9241,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9387,13 +9253,13 @@
         <v>150</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>78</v>
@@ -9402,15 +9268,15 @@
         <v>78</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9433,13 +9299,13 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9490,7 +9356,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9502,30 +9368,30 @@
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>448</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9548,13 +9414,13 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9605,7 +9471,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9617,30 +9483,30 @@
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>448</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9663,16 +9529,16 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9722,7 +9588,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9734,30 +9600,30 @@
         <v>150</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9780,16 +9646,16 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9839,7 +9705,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9851,19 +9717,19 @@
         <v>150</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -9871,10 +9737,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9897,16 +9763,16 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9956,7 +9822,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9971,10 +9837,10 @@
         <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9983,15 +9849,15 @@
         <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10014,16 +9880,16 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10073,7 +9939,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10082,16 +9948,16 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>478</v>
+        <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -10105,10 +9971,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10131,13 +9997,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10188,7 +10054,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10206,13 +10072,13 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -10220,10 +10086,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10335,10 +10201,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10452,14 +10318,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10481,10 +10347,10 @@
         <v>109</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>112</v>
@@ -10539,7 +10405,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10571,10 +10437,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10597,13 +10463,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10654,7 +10520,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>88</v>
@@ -10672,7 +10538,7 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
@@ -10686,10 +10552,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10712,16 +10578,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10750,10 +10616,10 @@
         <v>157</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -10771,7 +10637,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10789,24 +10655,24 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10829,16 +10695,16 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10867,10 +10733,10 @@
         <v>157</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -10888,7 +10754,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10906,24 +10772,24 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10946,16 +10812,16 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11005,7 +10871,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11017,19 +10883,19 @@
         <v>150</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -11037,14 +10903,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11063,16 +10929,16 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11122,7 +10988,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11134,13 +11000,13 @@
         <v>150</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
@@ -11154,10 +11020,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11180,16 +11046,16 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11239,7 +11105,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11251,13 +11117,13 @@
         <v>150</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>
